--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -48,10 +48,11 @@
     <sheet name="Зависимости стрима" sheetId="44" r:id="rId44"/>
     <sheet name="ROAM" sheetId="45" r:id="rId45"/>
     <sheet name="Scrum of Scrums" sheetId="46" r:id="rId46"/>
-    <sheet name="System Demo" sheetId="47" r:id="rId47"/>
-    <sheet name="Team Health Check" sheetId="48" r:id="rId48"/>
-    <sheet name="Деплои" sheetId="49" r:id="rId49"/>
-    <sheet name="Инциденты" sheetId="50" r:id="rId50"/>
+    <sheet name="Срезы стрима" sheetId="47" r:id="rId47"/>
+    <sheet name="System Demo" sheetId="48" r:id="rId48"/>
+    <sheet name="Team Health Check" sheetId="49" r:id="rId49"/>
+    <sheet name="Деплои" sheetId="50" r:id="rId50"/>
+    <sheet name="Инциденты" sheetId="51" r:id="rId51"/>
   </sheets>
 </workbook>
 </file>
@@ -10198,183 +10199,81 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">PI</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
+          <t xml:space="preserve">Итерация</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итерация</t>
+          <t xml:space="preserve">Дата</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t xml:space="preserve">Velocity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фича</t>
+          <t xml:space="preserve">Health</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Команды</t>
+          <t xml:space="preserve">Предсказуемость PI</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Докладчик</t>
+          <t xml:space="preserve">Say/Do</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итог</t>
+          <t xml:space="preserve">Баги</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отзывы</t>
+          <t xml:space="preserve">Блокеры</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-14</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-05</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Орлов Д.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Готово к релизу</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SD-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-01</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость устраивает</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SD-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-03</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поиск</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Смирнов К.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доработать</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
-        </is>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>89</v>
+      </c>
+      <c r="E2">
+        <v>0.42</v>
+      </c>
+      <c r="F2">
+        <v>0.89</v>
+      </c>
+      <c r="G2">
+        <v>0.71</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10392,417 +10291,177 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итерация</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Дата</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Спринт</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Измерение</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тренд</t>
+          <t xml:space="preserve">Команды</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комментарий</t>
+          <t xml:space="preserve">Докладчик</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итог</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отзывы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-01</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поставка ценности</t>
+          <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t xml:space="preserve">F-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Растёт</t>
+          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регулярные демо принимаются</t>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово к релизу</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-02</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Простота работы</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый</t>
+          <t xml:space="preserve">F-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стабильно</t>
+          <t xml:space="preserve">Корзина и оплата</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Много ручной рутины</t>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость устраивает</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-03</t>
+          <t xml:space="preserve">SD-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t xml:space="preserve">F-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Растёт</t>
+          <t xml:space="preserve">Поиск</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Парное программирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Миссия</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Цель понятна всем</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Командная работа</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Растёт</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Хорошая взаимопомощь</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поддержка и помощь</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Внешние зависимости тормозят</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пешки или игроки</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда влияет на решения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Блокеры по оплате</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подходящий процесс</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scrum устоялся</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Здоровье кодовой базы</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Красный</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Весело</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда мотивирована</t>
+          <t xml:space="preserve">Смирнов К.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доработать</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
         </is>
       </c>
     </row>
@@ -10826,22 +10485,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Релиз</t>
+          <t xml:space="preserve">Спринт</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Среда</t>
+          <t xml:space="preserve">Измерение</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Оценка</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lead time (дн)</t>
+          <t xml:space="preserve">Тренд</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -10853,210 +10512,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-01</t>
+          <t xml:space="preserve">HC-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Поставка ценности</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>3</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каркас каталога</t>
+          <t xml:space="preserve">Регулярные демо принимаются</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-02</t>
+          <t xml:space="preserve">HC-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Простота работы</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>2.2</v>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина</t>
+          <t xml:space="preserve">Много ручной рутины</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-03</t>
+          <t xml:space="preserve">HC-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage</t>
+          <t xml:space="preserve">Обучение</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>1.4</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оплата (пилот)</t>
+          <t xml:space="preserve">Парное программирование</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-04</t>
+          <t xml:space="preserve">HC-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Миссия</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Откат</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>2.8</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+          <t xml:space="preserve">Цель понятна всем</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-05</t>
+          <t xml:space="preserve">HC-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Командная работа</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.6</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Хотфикс оплаты</t>
+          <t xml:space="preserve">Хорошая взаимопомощь</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-06</t>
+          <t xml:space="preserve">HC-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-2</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Поддержка и помощь</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>1.9</v>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уведомления</t>
+          <t xml:space="preserve">Внешние зависимости тормозят</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пешки или игроки</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда влияет на решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блокеры по оплате</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подходящий процесс</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum устоялся</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Здоровье кодовой базы</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Весело</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда мотивирована</t>
         </is>
       </c>
     </row>
@@ -11229,6 +11063,260 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Релиз</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Среда</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead time (дн)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каркас каталога</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2.2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата (пилот)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>2.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хотфикс оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>1.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Инцидент</t>
         </is>
       </c>

--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -49,10 +49,12 @@
     <sheet name="ROAM" sheetId="45" r:id="rId45"/>
     <sheet name="Scrum of Scrums" sheetId="46" r:id="rId46"/>
     <sheet name="Срезы стрима" sheetId="47" r:id="rId47"/>
-    <sheet name="System Demo" sheetId="48" r:id="rId48"/>
-    <sheet name="Team Health Check" sheetId="49" r:id="rId49"/>
-    <sheet name="Деплои" sheetId="50" r:id="rId50"/>
-    <sheet name="Инциденты" sheetId="51" r:id="rId51"/>
+    <sheet name="Зрелость стрима" sheetId="48" r:id="rId48"/>
+    <sheet name="Улучшения стрима" sheetId="49" r:id="rId49"/>
+    <sheet name="System Demo" sheetId="50" r:id="rId50"/>
+    <sheet name="Team Health Check" sheetId="51" r:id="rId51"/>
+    <sheet name="Деплои" sheetId="52" r:id="rId52"/>
+    <sheet name="Инциденты" sheetId="53" r:id="rId53"/>
   </sheets>
 </workbook>
 </file>
@@ -10286,182 +10288,314 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">PI</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
+          <t xml:space="preserve">Измерение</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итерация</t>
+          <t xml:space="preserve">Голоса команд</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t xml:space="preserve">Медиана</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фича</t>
+          <t xml:space="preserve">Итог RTE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Команды</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Докладчик</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Итог</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отзывы</t>
+          <t xml:space="preserve">Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-01</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-14</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-05</t>
-        </is>
+          <t xml:space="preserve">PI-планирование</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Орлов Д.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Готово к релизу</t>
+          <t xml:space="preserve">Предсказуемость 89%, цели с бизнес-ценностью у всех команд</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-01</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-01</t>
-        </is>
+          <t xml:space="preserve">Синхронизация каденции</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 4; Поиск: 4; Мобильное приложение: 4</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость устраивает</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-02</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Бэклог фич</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 3; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Межкомандные зависимости</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 2; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 2</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System Demo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect &amp; Adapt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 2; Каталог: 3; Личный кабинет: 2; Поиск: 2; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-03</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поиск</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Смирнов К.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доработать</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Улучшения после I&amp;A не доводятся до конца</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Роли стрима</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 4</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Непрерывная поставка</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Технические практики</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 4; Мобильное приложение: 2</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Метрики и прозрачность</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -10480,417 +10614,91 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t xml:space="preserve">Измерение</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спринт</t>
+          <t xml:space="preserve">Действие</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Измерение</t>
+          <t xml:space="preserve">Владелец</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка</t>
+          <t xml:space="preserve">PI</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тренд</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Комментарий</t>
+          <t xml:space="preserve">Статус</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-01</t>
+          <t xml:space="preserve">MA-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>3</v>
+          <t xml:space="preserve">Inspect &amp; Adapt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вести бэклог улучшений I&amp;A с владельцами и сроками</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поставка ценности</t>
+          <t xml:space="preserve">RTE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Растёт</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Регулярные демо принимаются</t>
+          <t xml:space="preserve">В работе</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-02</t>
+          <t xml:space="preserve">MA-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>3</v>
+          <t xml:space="preserve">Технические практики</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Единый DoD стрима: автотесты и ревью обязательны</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Простота работы</t>
+          <t xml:space="preserve">Архитектор</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Много ручной рутины</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Обучение</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Растёт</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Парное программирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Миссия</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Цель понятна всем</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Командная работа</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Растёт</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Хорошая взаимопомощь</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поддержка и помощь</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Внешние зависимости тормозят</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пешки или игроки</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда влияет на решения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Блокеры по оплате</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подходящий процесс</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scrum устоялся</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Здоровье кодовой базы</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Красный</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Весело</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда мотивирована</t>
+          <t xml:space="preserve">Запланировано</t>
         </is>
       </c>
     </row>
@@ -11058,242 +10866,177 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итерация</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Дата</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Релиз</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Среда</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lead time (дн)</t>
+          <t xml:space="preserve">Команды</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комментарий</t>
+          <t xml:space="preserve">Докладчик</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итог</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отзывы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-01</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>3</v>
+          <t xml:space="preserve">F-05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каркас каталога</t>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово к релизу</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-02</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>2.2</v>
+          <t xml:space="preserve">F-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина</t>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость устраивает</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-03</t>
+          <t xml:space="preserve">SD-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>1.4</v>
+          <t xml:space="preserve">F-03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поиск</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оплата (пилот)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DP-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prod</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Откат</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>2.8</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DP-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prod</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Хотфикс оплаты</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DP-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prod</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>1.9</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Уведомления</t>
+          <t xml:space="preserve">Смирнов К.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доработать</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
         </is>
       </c>
     </row>
@@ -11317,6 +11060,689 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Измерение</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оценка</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тренд</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поставка ценности</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Регулярные демо принимаются</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Простота работы</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Много ручной рутины</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обучение</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Парное программирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Миссия</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Цель понятна всем</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Командная работа</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хорошая взаимопомощь</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддержка и помощь</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешние зависимости тормозят</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пешки или игроки</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда влияет на решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блокеры по оплате</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подходящий процесс</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum устоялся</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Здоровье кодовой базы</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Весело</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда мотивирована</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Релиз</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Среда</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead time (дн)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каркас каталога</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2.2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата (пилот)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>2.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хотфикс оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>1.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Инцидент</t>
         </is>
       </c>

--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -10245,39 +10245,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-10</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>89</v>
-      </c>
-      <c r="E2">
-        <v>0.42</v>
-      </c>
-      <c r="F2">
-        <v>0.89</v>
-      </c>
-      <c r="G2">
-        <v>0.71</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -43,18 +43,19 @@
     <sheet name="Planning Poker" sheetId="39" r:id="rId39"/>
     <sheet name="Портфель" sheetId="40" r:id="rId40"/>
     <sheet name="Стримы и команды" sheetId="41" r:id="rId41"/>
-    <sheet name="Фичи стрима" sheetId="42" r:id="rId42"/>
-    <sheet name="Цели PI" sheetId="43" r:id="rId43"/>
-    <sheet name="Зависимости стрима" sheetId="44" r:id="rId44"/>
-    <sheet name="ROAM" sheetId="45" r:id="rId45"/>
-    <sheet name="Scrum of Scrums" sheetId="46" r:id="rId46"/>
-    <sheet name="Срезы стрима" sheetId="47" r:id="rId47"/>
-    <sheet name="Зрелость стрима" sheetId="48" r:id="rId48"/>
-    <sheet name="Улучшения стрима" sheetId="49" r:id="rId49"/>
-    <sheet name="System Demo" sheetId="50" r:id="rId50"/>
-    <sheet name="Team Health Check" sheetId="51" r:id="rId51"/>
-    <sheet name="Деплои" sheetId="52" r:id="rId52"/>
-    <sheet name="Инциденты" sheetId="53" r:id="rId53"/>
+    <sheet name="Команда управления" sheetId="42" r:id="rId42"/>
+    <sheet name="Фичи стрима" sheetId="43" r:id="rId43"/>
+    <sheet name="Цели PI" sheetId="44" r:id="rId44"/>
+    <sheet name="Зависимости стрима" sheetId="45" r:id="rId45"/>
+    <sheet name="ROAM" sheetId="46" r:id="rId46"/>
+    <sheet name="Scrum of Scrums" sheetId="47" r:id="rId47"/>
+    <sheet name="Срезы стрима" sheetId="48" r:id="rId48"/>
+    <sheet name="Зрелость стрима" sheetId="49" r:id="rId49"/>
+    <sheet name="Улучшения стрима" sheetId="50" r:id="rId50"/>
+    <sheet name="System Demo" sheetId="51" r:id="rId51"/>
+    <sheet name="Team Health Check" sheetId="52" r:id="rId52"/>
+    <sheet name="Деплои" sheetId="53" r:id="rId53"/>
+    <sheet name="Инциденты" sheetId="54" r:id="rId54"/>
   </sheets>
 </workbook>
 </file>
@@ -9039,328 +9040,199 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Стрим</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фича</t>
+          <t xml:space="preserve">Должность</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Сотрудник</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Владелец</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BV</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RR</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Размер</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WSJF</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Историй</t>
+          <t xml:space="preserve">Права</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-01</t>
+          <t xml:space="preserve">Стрим «Покупки»</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оплата картой и СБП</t>
+          <t xml:space="preserve">Лидер стрима</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В работе</t>
+          <t xml:space="preserve">Петрова М.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>4.2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
+          <t xml:space="preserve">стрим и все команды</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-02</t>
+          <t xml:space="preserve">Стрим «Покупки»</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Персональные рекомендации</t>
+          <t xml:space="preserve">ИТ-лидер стрима</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ</t>
+          <t xml:space="preserve">Смирнов К.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Иванов А.</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>1.5</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+          <t xml:space="preserve">стрим и все команды</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-03</t>
+          <t xml:space="preserve">Стрим «Покупки»</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Быстрый поиск по каталогу</t>
+          <t xml:space="preserve">Архитектор</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">В работе</t>
+          <t xml:space="preserve">Кузнецова Е.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Смирнов К.</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>4.7</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+          <t xml:space="preserve">данные стрима, команды — просмотр</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-04</t>
+          <t xml:space="preserve">Стрим «Покупки»</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Единый личный кабинет</t>
+          <t xml:space="preserve">Проектный менеджер</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бэклог</t>
+          <t xml:space="preserve">Орлов Д.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Кузнецова Е.</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+          <t xml:space="preserve">данные стрима, команды — просмотр</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-05</t>
+          <t xml:space="preserve">Стрим «Логистика»</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push-уведомления о заказе</t>
+          <t xml:space="preserve">Лидер стрима</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Готово</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Орлов Д.</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
+          <t xml:space="preserve">стрим и все команды</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-06</t>
+          <t xml:space="preserve">Стрим «Логистика»</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подписка на доставку</t>
+          <t xml:space="preserve">ИТ-лидер стрима</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Воронка</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI 2026.4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>0.9</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+          <t xml:space="preserve">стрим и все команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стрим «Логистика»</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Архитектор</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">данные стрима, команды — просмотр</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стрим «Логистика»</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проектный менеджер</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">данные стрима, команды — просмотр</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9378,200 +9250,323 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Цель</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">BV план</t>
+          <t xml:space="preserve">Владелец</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">BV факт</t>
+          <t xml:space="preserve">BV</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обязательная</t>
+          <t xml:space="preserve">TC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Размер</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WSJF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Историй</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-01</t>
+          <t xml:space="preserve">F-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Оплата картой и СБП</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Запустить оплату картой и СБП</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>9</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
       </c>
       <c r="F2">
         <v>8</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>4.2</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-02</t>
+          <t xml:space="preserve">F-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Персональные рекомендации</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анализ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поиск</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поиск по каталогу быстрее 300 мс</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>7</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-03</t>
+          <t xml:space="preserve">F-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Быстрый поиск по каталогу</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Каталог</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Фильтры и сортировка каталога</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>6</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Смирнов К.</t>
+        </is>
       </c>
       <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>4.7</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-04</t>
+          <t xml:space="preserve">F-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Единый личный кабинет</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бэклог</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мобильное приложение</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Push-уведомления о заказе</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>5</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецова Е.</t>
+        </is>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-05</t>
+          <t xml:space="preserve">F-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Push-уведомления о заказе</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Личный кабинет</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рекомендации на главной</t>
-        </is>
-      </c>
-      <c r="E6">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">нет</t>
-        </is>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подписка на доставку</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Воронка</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>0.9</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9589,49 +9584,44 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто ждёт</t>
+          <t xml:space="preserve">PI</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто делает</t>
+          <t xml:space="preserve">Команда</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фича</t>
+          <t xml:space="preserve">Цель</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что нужно</t>
+          <t xml:space="preserve">BV план</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нужно к итерации</t>
+          <t xml:space="preserve">BV факт</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">План итерации</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Обязательная</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XD-01</t>
+          <t xml:space="preserve">O-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильное приложение</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9641,35 +9631,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API платежей для мобильного экрана</t>
-        </is>
+          <t xml:space="preserve">Запустить оплату картой и СБП</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принята</t>
+        <v>8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">XD-02</t>
+          <t xml:space="preserve">O-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каталог</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9679,35 +9664,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-03</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Индекс товаров для фильтров</t>
-        </is>
+          <t xml:space="preserve">Поиск по каталогу быстрее 300 мс</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Выполнена</t>
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">XD-03</t>
+          <t xml:space="preserve">O-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Личный кабинет</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9717,35 +9697,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-04</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Справочник категорий</t>
-        </is>
+          <t xml:space="preserve">Фильтры и сортировка каталога</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Открыта</t>
+        <v>5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">XD-04</t>
+          <t xml:space="preserve">O-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина и оплата</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9755,23 +9730,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">F-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDK уведомлений</t>
-        </is>
+          <t xml:space="preserve">Push-уведомления о заказе</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Заблокирована</t>
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Личный кабинет</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рекомендации на главной</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нет</t>
         </is>
       </c>
     </row>
@@ -9790,49 +9795,49 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Риск</t>
+          <t xml:space="preserve">Кто ждёт</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Команда</t>
+          <t xml:space="preserve">Кто делает</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Влияние</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROAM</t>
+          <t xml:space="preserve">Что нужно</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Владелец</t>
+          <t xml:space="preserve">Нужно к итерации</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Срок</t>
+          <t xml:space="preserve">План итерации</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Решение</t>
+          <t xml:space="preserve">Статус</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-01</t>
+          <t xml:space="preserve">XD-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сертификация PCI DSS может не успеть к релизу</t>
+          <t xml:space="preserve">Мобильное приложение</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9842,39 +9847,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Высокое</t>
+          <t xml:space="preserve">F-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owned</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-11-20</t>
-        </is>
+          <t xml:space="preserve">API платежей для мобильного экрана</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ранний аудит, выделенный инженер по безопасности</t>
+          <t xml:space="preserve">Принята</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-02</t>
+          <t xml:space="preserve">XD-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нагрузка на поиск в распродажу</t>
+          <t xml:space="preserve">Каталог</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9884,111 +9885,99 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Высокое</t>
+          <t xml:space="preserve">F-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mitigated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Смирнов К.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-30</t>
-        </is>
+          <t xml:space="preserve">Индекс товаров для фильтров</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кэш и нагрузочное тестирование</t>
+          <t xml:space="preserve">Выполнена</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-03</t>
+          <t xml:space="preserve">XD-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зависимость мобильной команды от API платежей</t>
+          <t xml:space="preserve">Личный кабинет</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильное приложение</t>
+          <t xml:space="preserve">Каталог</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Среднее</t>
+          <t xml:space="preserve">F-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Орлов Д.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">Справочник категорий</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заглушка API до итерации 4</t>
+          <t xml:space="preserve">Открыта</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-04</t>
+          <t xml:space="preserve">XD-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нехватка дизайнера в стриме</t>
+          <t xml:space="preserve">Корзина и оплата</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стрим</t>
+          <t xml:space="preserve">Мобильное приложение</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Среднее</t>
+          <t xml:space="preserve">F-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RTE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">SDK уведомлений</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дизайнер привлечён из «Логистики»</t>
+          <t xml:space="preserve">Заблокирована</t>
         </is>
       </c>
     </row>
@@ -10002,192 +9991,210 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Риск</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Команда</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сделано / прогресс</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планы</t>
+          <t xml:space="preserve">Влияние</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Блокеры</t>
+          <t xml:space="preserve">ROAM</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нужна помощь от</t>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Срок</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решение</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">R-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Сертификация PCI DSS может не успеть к релизу</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Корзина и оплата</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Спринт #3: 0 из 32 SP, риск — высокий</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Довести СБП до стенда</t>
+          <t xml:space="preserve">Высокое</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+          <t xml:space="preserve">Owned</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильное приложение</t>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-11-20</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ранний аудит, выделенный инженер по безопасности</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">R-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каталог</t>
+          <t xml:space="preserve">Нагрузка на поиск в распродажу</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спринт #3: 10 из 32 SP, риск — средний</t>
+          <t xml:space="preserve">Поиск</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фильтры — в ревью</t>
+          <t xml:space="preserve">Высокое</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+          <t xml:space="preserve">Mitigated</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Смирнов К.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кэш и нагрузочное тестирование</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">R-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Личный кабинет</t>
+          <t xml:space="preserve">Зависимость мобильной команды от API платежей</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спринт #3: 8 из 29 SP, риск — высокий</t>
+          <t xml:space="preserve">Мобильное приложение</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Макеты кабинета</t>
+          <t xml:space="preserve">Среднее</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+          <t xml:space="preserve">Accepted</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каталог</t>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Заглушка API до итерации 4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">R-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поиск</t>
+          <t xml:space="preserve">Нехватка дизайнера в стриме</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Спринт #3: 11 из 29 SP, риск — средний</t>
+          <t xml:space="preserve">Стрим</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индекс — в прод</t>
+          <t xml:space="preserve">Среднее</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+          <t xml:space="preserve">Resolved</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мобильное приложение</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Спринт #3: 10 из 32 SP, риск — средний</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Экран оплаты на заглушке</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата</t>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дизайнер привлечён из «Логистики»</t>
         </is>
       </c>
     </row>
@@ -10201,47 +10208,192 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
+          <t xml:space="preserve">Дата</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итерация</t>
+          <t xml:space="preserve">Команда</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t xml:space="preserve">Сделано / прогресс</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velocity</t>
+          <t xml:space="preserve">Планы</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health</t>
+          <t xml:space="preserve">Блокеры</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Предсказуемость PI</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Say/Do</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Баги</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Блокеры</t>
+          <t xml:space="preserve">Нужна помощь от</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт #3: 0 из 32 SP, риск — высокий</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Довести СБП до стенда</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мобильное приложение</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каталог</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт #3: 10 из 32 SP, риск — средний</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фильтры — в ревью</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт #3: 8 из 29 SP, риск — высокий</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Макеты кабинета</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каталог</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поиск</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт #3: 11 из 29 SP, риск — средний</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Индекс — в прод</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мобильное приложение</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт #3: 10 из 32 SP, риск — средний</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экран оплаты на заглушке</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера; Стенд нестабилен (падает ночью); Интеграция платежей; Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата</t>
         </is>
       </c>
     </row>
@@ -10260,309 +10412,42 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Измерение</t>
+          <t xml:space="preserve">Итерация</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Голоса команд</t>
+          <t xml:space="preserve">Дата</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медиана</t>
+          <t xml:space="preserve">Velocity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итог RTE</t>
+          <t xml:space="preserve">Health</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI-планирование</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Предсказуемость 89%, цели с бизнес-ценностью у всех команд</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Синхронизация каденции</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 4; Поиск: 4; Мобильное приложение: 4</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Бэклог фич</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 3; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Межкомандные зависимости</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 2; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 2</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">System Demo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspect &amp; Adapt</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 2; Каталог: 3; Личный кабинет: 2; Поиск: 2; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Улучшения после I&amp;A не доводятся до конца</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Роли стрима</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 4</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Непрерывная поставка</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Технические практики</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 4; Мобильное приложение: 2</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Метрики и прозрачность</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Предсказуемость PI</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Say/Do</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Баги</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блокеры</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10461,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">PI</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -10586,86 +10471,304 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Действие</t>
+          <t xml:space="preserve">Голоса команд</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Владелец</t>
+          <t xml:space="preserve">Медиана</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
+          <t xml:space="preserve">Итог RTE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA-01</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect &amp; Adapt</t>
+          <t xml:space="preserve">PI-планирование</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вести бэклог улучшений I&amp;A с владельцами и сроками</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RTE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В работе</t>
+          <t xml:space="preserve">Предсказуемость 89%, цели с бизнес-ценностью у всех команд</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MA-02</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Синхронизация каденции</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 4; Поиск: 4; Мобильное приложение: 4</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бэклог фич</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 3; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Межкомандные зависимости</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 2; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 2</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System Demo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect &amp; Adapt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 2; Каталог: 3; Личный кабинет: 2; Поиск: 2; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Улучшения после I&amp;A не доводятся до конца</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда управления стрима</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 3; Поиск: 3; Мобильное приложение: 4</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Непрерывная поставка</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 4; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI 2026.3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Технические практики</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Единый DoD стрима: автотесты и ревью обязательны</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Архитектор</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 3; Каталог: 3; Личный кабинет: 2; Поиск: 4; Мобильное приложение: 2</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Запланировано</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Метрики и прозрачность</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина и оплата: 4; Каталог: 3; Личный кабинет: 3; Поиск: 4; Мобильное приложение: 3</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -10833,177 +10936,91 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Измерение</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Действие</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Итерация</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дата</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Фича</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Команды</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Докладчик</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Итог</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отзывы</t>
+          <t xml:space="preserve">Статус</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-01</t>
+          <t xml:space="preserve">MA-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspect &amp; Adapt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вести бэклог улучшений I&amp;A с владельцами и сроками</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Орлов Д. (ПМ)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-14</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-05</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Орлов Д.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Готово к релизу</t>
+          <t xml:space="preserve">В работе</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD-01</t>
+          <t xml:space="preserve">MA-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Технические практики</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Единый DoD стрима: автотесты и ревью обязательны</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Архитектор</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-01</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина и оплата</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Петрова М.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Принято</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость устраивает</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SD-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI 2026.3</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F-03</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поиск</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Смирнов К.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Доработать</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
+          <t xml:space="preserve">Запланировано</t>
         </is>
       </c>
     </row>
@@ -11022,417 +11039,177 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итерация</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Дата</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Спринт</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Измерение</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тренд</t>
+          <t xml:space="preserve">Команды</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комментарий</t>
+          <t xml:space="preserve">Докладчик</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итог</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отзывы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-01</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поставка ценности</t>
+          <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t xml:space="preserve">F-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Растёт</t>
+          <t xml:space="preserve">Мобильное приложение, Корзина и оплата</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регулярные демо принимаются</t>
+          <t xml:space="preserve">Орлов Д.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово к релизу</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-02</t>
+          <t xml:space="preserve">SD-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Простота работы</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый</t>
+          <t xml:space="preserve">F-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стабильно</t>
+          <t xml:space="preserve">Корзина и оплата</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Много ручной рутины</t>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость устраивает</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HC-03</t>
+          <t xml:space="preserve">SD-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">PI 2026.3</t>
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение</t>
+          <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t xml:space="preserve">F-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Растёт</t>
+          <t xml:space="preserve">Поиск</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Парное программирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Миссия</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Цель понятна всем</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Командная работа</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Растёт</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Хорошая взаимопомощь</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Поддержка и помощь</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Внешние зависимости тормозят</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пешки или игроки</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда влияет на решения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Скорость</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Жёлтый</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Блокеры по оплате</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подходящий процесс</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scrum устоялся</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Здоровье кодовой базы</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Красный</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Падает</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HC-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Весело</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Зелёный</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Стабильно</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Команда мотивирована</t>
+          <t xml:space="preserve">Смирнов К.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Доработать</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нужен экран ошибок оплаты</t>
         </is>
       </c>
     </row>
@@ -11456,22 +11233,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Релиз</t>
+          <t xml:space="preserve">Спринт</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Среда</t>
+          <t xml:space="preserve">Измерение</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статус</t>
+          <t xml:space="preserve">Оценка</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lead time (дн)</t>
+          <t xml:space="preserve">Тренд</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -11483,210 +11260,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-01</t>
+          <t xml:space="preserve">HC-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Поставка ценности</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>3</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каркас каталога</t>
+          <t xml:space="preserve">Регулярные демо принимаются</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-02</t>
+          <t xml:space="preserve">HC-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Простота работы</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>2.2</v>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корзина</t>
+          <t xml:space="preserve">Много ручной рутины</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-03</t>
+          <t xml:space="preserve">HC-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage</t>
+          <t xml:space="preserve">Обучение</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>1.4</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оплата (пилот)</t>
+          <t xml:space="preserve">Парное программирование</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-04</t>
+          <t xml:space="preserve">HC-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Миссия</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Откат</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>2.8</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+          <t xml:space="preserve">Цель понятна всем</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-05</t>
+          <t xml:space="preserve">HC-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-1</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Командная работа</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.6</v>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Хотфикс оплаты</t>
+          <t xml:space="preserve">Хорошая взаимопомощь</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP-06</t>
+          <t xml:space="preserve">HC-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R-2</t>
-        </is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prod</t>
+          <t xml:space="preserve">Поддержка и помощь</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Успех</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>1.9</v>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Уведомления</t>
+          <t xml:space="preserve">Внешние зависимости тормозят</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пешки или игроки</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда влияет на решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блокеры по оплате</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подходящий процесс</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum устоялся</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Здоровье кодовой базы</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Весело</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда мотивирована</t>
         </is>
       </c>
     </row>
@@ -11710,6 +11662,260 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Релиз</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Среда</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead time (дн)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каркас каталога</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2.2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата (пилот)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>2.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хотфикс оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>1.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Инцидент</t>
         </is>
       </c>

--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -6624,12 +6624,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-21</t>
+          <t xml:space="preserve">FE-1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[F-01] Платёжный шлюз</t>
+          <t xml:space="preserve">Фича: Корзина и заказ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6644,19 +6644,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">История</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Готово</t>
+          <t xml:space="preserve">В работе</t>
         </is>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -6677,12 +6677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-22</t>
+          <t xml:space="preserve">FE-2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">[F-01] Оплата через СБП</t>
+          <t xml:space="preserve">Фича: Онлайн-оплата</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6697,11 +6697,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">История</t>
+          <t xml:space="preserve">Фича</t>
         </is>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -6730,51 +6730,263 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Каталог и рекомендации</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[F-01] Платёжный шлюз</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[F-01] Оплата через СБП</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t xml:space="preserve">T-23</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">[F-05] События заказа для push</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">История</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="F30">
         <v>2</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">Готово</t>
         </is>
       </c>
-      <c r="H26">
+      <c r="H30">
         <v>1</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/Управление_стримами_и_командами.xlsx
+++ b/Управление_стримами_и_командами.xlsx
@@ -56,6 +56,7 @@
     <sheet name="Team Health Check" sheetId="52" r:id="rId52"/>
     <sheet name="Деплои" sheetId="53" r:id="rId53"/>
     <sheet name="Инциденты" sheetId="54" r:id="rId54"/>
+    <sheet name="Гант по иерархии" sheetId="55" r:id="rId55"/>
   </sheets>
 </workbook>
 </file>
@@ -12281,6 +12282,5055 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уровень</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тип</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Название</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Родитель</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зависит от</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Исполнитель</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">План: начало</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">План: конец</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Факт: начало</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Факт: конец</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Объём, SP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово, SP</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прогресс</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Просрочено</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовый план: начало</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовый план: конец</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сдвиг, дн.</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прогноз завершения</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало бизнес-анализа</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бизнес-анализ пройден</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало системного анализа</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Системный анализ пройден</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало разработки</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разработка завершена</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало ИФТ (интеграционно-функциональное тестирование)</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ИФТ завершено</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало ПСИ (приёмо-сдаточные испытания)</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПСИ завершено</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало выхода в Прод</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выход в Прод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Оформление и оплата заказа</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N2">
+        <v>53</v>
+      </c>
+      <c r="O2">
+        <v>30</v>
+      </c>
+      <c r="P2">
+        <v>0.57</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.10.2026</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.2026</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Корзина и заказ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N3">
+        <v>23</v>
+      </c>
+      <c r="O3">
+        <v>13</v>
+      </c>
+      <c r="P3">
+        <v>0.57</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.10.2026</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.2026</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.07.2026</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проектирование API заказов</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.2026</t>
+        </is>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.2026</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модель данных заказа</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История заказов</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соколов Р.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экран корзины (вёрстка)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.08.2026</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.08.2026</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.08.2026</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.08.2026</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Онлайн-оплата</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>30</v>
+      </c>
+      <c r="O8">
+        <v>17</v>
+      </c>
+      <c r="P8">
+        <v>0.57</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29.09.2026</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.07.2026</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API промокодов</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Козлов В.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>9</v>
+      </c>
+      <c r="O9">
+        <v>9</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления по e-mail</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Смирнов П.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.08.2026</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.08.2026</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вебхуки платежей</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>13</v>
+      </c>
+      <c r="O11">
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <v>0.62</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Интеграция платежей</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>8</v>
+      </c>
+      <c r="O12">
+        <v>8</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экран оплаты</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Волкова Н.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.09.2026</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.09.2026</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Каталог и личный кабинет</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>43</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Личный кабинет</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>11</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рефакторинг авторизации</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Личный кабинет</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Волкова Н.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17">
+        <v>8</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Каталог и рекомендации</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18">
+        <v>27</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Аналитика воронки</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Орлова Е.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фильтры каталога</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Морозов И.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20">
+        <v>11</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тех.долг</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отзывы и рейтинги</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-17</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лебедева Т.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рекомендации</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фёдорова О.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.09.2026</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22">
+        <v>13</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.10.2026</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/B тесты чекаута</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-19</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Морозов И.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.09.2026</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.10.2026</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Регресс-тестирование релиза</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сидоров К.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича стрима: Оплата картой и СБП</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25">
+        <v>8</v>
+      </c>
+      <c r="O25">
+        <v>5</v>
+      </c>
+      <c r="P25">
+        <v>0.63</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[F-01] Платёжный шлюз</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
+        <v>5</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[F-01] Оплата через СБП</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича стрима: Push-уведомления о заказе</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[F-05] События заказа для push</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка CI/CD</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новиков А.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тех.долг</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тест-кейсы оформления</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сидоров К.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.08.2026</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.08.2026</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>4</v>
+      </c>
+      <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.08.2026</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.08.2026</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новиков А.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
